--- a/config/battle_card_halo.xlsx
+++ b/config/battle_card_halo.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="battle_card_halo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="battle_card_halo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>異なる属性の仲間を6体編成</t>
+          <t>6个不同属性的伙伴组成</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1383,7 +1383,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
@@ -1419,7 +1418,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,7 +1432,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>同属性の仲間を3体編成</t>
+          <t>3个同属性的伙伴组成</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1472,7 +1470,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>2</t>
@@ -1508,7 +1505,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1523,7 +1519,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>同属性の仲間を2体ずつ編成</t>
+          <t>将同属性的伙伴每2只编成</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1561,7 +1557,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1597,7 +1592,6 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1612,7 +1606,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>同属性の仲間を3体ずつ編成</t>
+          <t>将同属性的伙伴每3只编成</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1690,7 +1684,6 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1705,7 +1698,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>同属性の仲間4体と、同属性の仲間2体を編成</t>
+          <t>组成4个同属性的伙伴和2个同属性的伙伴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1783,7 +1776,6 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1798,7 +1790,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>同属性の仲間を6体編成</t>
+          <t>6个同属性的伙伴组成</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1876,10 +1868,8 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>config/embattle/icon_gh7.png</t>
@@ -1925,8 +1915,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>14</t>
@@ -1937,14 +1925,8 @@
           <t>500</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>config/embattle/icon_gh7.png</t>
@@ -1990,8 +1972,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>24</t>
@@ -2002,14 +1982,8 @@
           <t>500</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>config/embattle/icon_gh7.png</t>
@@ -2055,8 +2029,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>13</t>
@@ -2067,14 +2039,8 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>config/embattle/icon_gh7.png</t>
@@ -2120,8 +2086,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>15</t>
@@ -2132,11 +2096,6 @@
           <t>500</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
